--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484284_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484284_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4544</v>
+        <v>6.1331</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8584</v>
+        <v>3.829</v>
       </c>
       <c r="F2" t="n">
-        <v>1.596</v>
+        <v>2.3041</v>
       </c>
       <c r="G2" t="n">
         <v>6.4928</v>
@@ -610,13 +610,13 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6162</v>
+        <v>0.0625</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.1232</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7689</v>
+        <v>-0.0607</v>
       </c>
       <c r="V2" t="n">
         <v>0.5545</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3319</v>
+        <v>4.342</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1577</v>
+        <v>-0.0645</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1742</v>
+        <v>4.4065</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0849</v>
+        <v>7.0746</v>
       </c>
       <c r="H3" t="n">
-        <v>1.033</v>
+        <v>2.7854</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0519</v>
+        <v>4.2892</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8764</v>
+        <v>4.2033</v>
       </c>
       <c r="K3" t="n">
-        <v>0.903</v>
+        <v>1.1269</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0266</v>
+        <v>3.0764</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2085</v>
+        <v>2.8713</v>
       </c>
       <c r="N3" t="n">
-        <v>0.13</v>
+        <v>1.6585</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0786</v>
+        <v>1.2128</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R3" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7511</v>
+        <v>-0.0545</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3715</v>
+        <v>-0.3609</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3796</v>
+        <v>0.3065</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8865</v>
+        <v>-0.9201</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.9201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2897</v>
+        <v>3.1647</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0351</v>
+        <v>0.8544</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3248</v>
+        <v>2.3104</v>
       </c>
       <c r="G4" t="n">
-        <v>7.0746</v>
+        <v>2.0849</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7854</v>
+        <v>1.033</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2892</v>
+        <v>1.0519</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2033</v>
+        <v>0.8764</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1269</v>
+        <v>0.903</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0764</v>
+        <v>-0.0266</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8713</v>
+        <v>1.2085</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6585</v>
+        <v>0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2128</v>
+        <v>1.0786</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1067</v>
+        <v>0.5839</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3315</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2248</v>
+        <v>0.5158</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9201</v>
+        <v>0.8865</v>
       </c>
       <c r="W4" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.9201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6962</v>
+        <v>0.7143</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7042</v>
+        <v>-2.9224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.992</v>
+        <v>3.6367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4258</v>
+        <v>2.404</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.6624</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1352</v>
+        <v>0.7416</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0217</v>
+        <v>0.8061</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0217</v>
+        <v>0.0639</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.7422</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4041</v>
+        <v>1.5978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5393</v>
+        <v>1.5984</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1352</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8313</v>
+        <v>0.1856</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6592</v>
+        <v>-0.0989</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1722</v>
+        <v>0.2846</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3656</v>
+        <v>0.6642</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3656</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4023</v>
+        <v>0.7123</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.9258</v>
+        <v>-0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3282</v>
+        <v>1.0193</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2985</v>
+        <v>0.4258</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7536</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0521</v>
+        <v>-0.1352</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.1174</v>
+        <v>0.0217</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.5519</v>
+        <v>0.0217</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5655</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4159</v>
+        <v>0.4041</v>
       </c>
       <c r="N6" t="n">
-        <v>1.7982</v>
+        <v>0.5393</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6176</v>
+        <v>-0.1352</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.1022</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8603</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3781</v>
+        <v>0.8474</v>
       </c>
       <c r="T6" t="n">
-        <v>1.728</v>
+        <v>0.648</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6501</v>
+        <v>0.1994</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8279</v>
+        <v>-0.3656</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>-0.3656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1824</v>
+        <v>-1.0501</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7918</v>
+        <v>-5.0787</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6095</v>
+        <v>4.0286</v>
       </c>
       <c r="G7" t="n">
-        <v>2.404</v>
+        <v>0.2985</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6624</v>
+        <v>-0.7536</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7416</v>
+        <v>1.0521</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8061</v>
+        <v>-3.1174</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0639</v>
+        <v>-2.5519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7422</v>
+        <v>-0.5655</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5978</v>
+        <v>3.4159</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5984</v>
+        <v>1.7982</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>1.6176</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.5395</v>
+        <v>-4.1022</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9069</v>
+        <v>-5.8603</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.711</v>
+        <v>0.9257</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9684</v>
+        <v>0.5752</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2573</v>
+        <v>0.3505</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>3.3238</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3869</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4184</v>
+        <v>-1.6314</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7533</v>
+        <v>-1.0803</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1717</v>
+        <v>-0.5511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0237</v>
+        <v>0.0706</v>
       </c>
       <c r="H8" t="n">
-        <v>2.427</v>
+        <v>1.0016</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4033</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.313</v>
+        <v>0.7506</v>
       </c>
       <c r="K8" t="n">
-        <v>2.232</v>
+        <v>0.7368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>0.0138</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2893</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1949</v>
+        <v>0.2648</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4842</v>
+        <v>-0.9447</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8566</v>
+        <v>-0.0825</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4171</v>
+        <v>0.1225</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4395</v>
+        <v>-0.205</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.2987</v>
+        <v>-0.6428</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.2987</v>
+        <v>-0.6428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8412</v>
+        <v>-1.8713</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3182</v>
+        <v>-1.6494</v>
       </c>
       <c r="F9" t="n">
-        <v>1.477</v>
+        <v>-0.2219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9728</v>
+        <v>-2.2484</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0565</v>
+        <v>0.3671</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9163</v>
+        <v>-2.6155</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3456</v>
+        <v>-1.9733</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5884</v>
+        <v>0.1023</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2428</v>
+        <v>-2.0756</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3185</v>
+        <v>-0.2751</v>
       </c>
       <c r="N9" t="n">
-        <v>0.645</v>
+        <v>0.2648</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6735</v>
+        <v>-0.5399</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8036</v>
+        <v>-0.1988</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3798</v>
+        <v>0.0819</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4237</v>
+        <v>-0.2807</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8828</v>
+        <v>0.5758</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>-0.6428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4314</v>
+        <v>-2.6553</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.155</v>
+        <v>1.8433</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2764</v>
+        <v>-4.4986</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2484</v>
+        <v>1.0237</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3671</v>
+        <v>2.427</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6155</v>
+        <v>-1.4033</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9733</v>
+        <v>2.313</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1023</v>
+        <v>2.232</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0756</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2751</v>
+        <v>-1.2893</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2648</v>
+        <v>0.1949</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5399</v>
+        <v>-1.4842</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,28 +1234,28 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7588</v>
+        <v>0.6197</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4237</v>
+        <v>0.507</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3352</v>
+        <v>0.1127</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5758</v>
+        <v>-4.2987</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6428</v>
+        <v>-4.2987</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4832</v>
+        <v>-2.7376</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.687</v>
+        <v>-3.561</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7962</v>
+        <v>0.8234</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0706</v>
+        <v>0.9728</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0016</v>
+        <v>0.0565</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0.9163</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7506</v>
+        <v>-0.3456</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7368</v>
+        <v>-0.5884</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0138</v>
+        <v>0.2428</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6798999999999999</v>
+        <v>1.3185</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2648</v>
+        <v>0.645</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9447</v>
+        <v>0.6735</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9767</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9343</v>
+        <v>0.9071</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4842</v>
+        <v>0.137</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4502</v>
+        <v>0.7701</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6428</v>
+        <v>-1.8828</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6428</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.8179</v>
+        <v>5.120699999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.439299999999999</v>
+        <v>-8.136600000000001</v>
       </c>
       <c r="F12" t="n">
         <v>13.2574</v>
@@ -1363,16 +1363,16 @@
         <v>4.7196</v>
       </c>
       <c r="J12" t="n">
-        <v>8.6395</v>
+        <v>8.639500000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>5.936099999999999</v>
+        <v>5.936100000000001</v>
       </c>
       <c r="L12" t="n">
         <v>2.7034</v>
       </c>
       <c r="M12" t="n">
-        <v>9.959899999999999</v>
+        <v>9.959900000000001</v>
       </c>
       <c r="N12" t="n">
         <v>7.9435</v>
@@ -1390,19 +1390,19 @@
         <v>11.7206</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4937</v>
+        <v>3.7961</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5005</v>
+        <v>1.8031</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9929</v>
+        <v>1.9932</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6011</v>
       </c>
       <c r="W12" t="n">
-        <v>6.815099999999999</v>
+        <v>6.8151</v>
       </c>
       <c r="X12" t="n">
         <v>-10.4163</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9427</v>
+        <v>4.4916</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8508</v>
+        <v>1.3452</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0919</v>
+        <v>3.1464</v>
       </c>
       <c r="G13" t="n">
         <v>0.9782999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>4.2975</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0626</v>
+        <v>-0.5137</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5092</v>
+        <v>0.0037</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5718</v>
+        <v>-0.5174</v>
       </c>
       <c r="V13" t="n">
         <v>2.6596</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2264</v>
+        <v>3.5534</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7146</v>
+        <v>2.3233</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5118</v>
+        <v>1.2301</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1528</v>
+        <v>-0.2838</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1929</v>
+        <v>0.0926</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0401</v>
+        <v>-0.3764</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3982</v>
+        <v>-0.1245</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6526</v>
+        <v>1.3303</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2544</v>
+        <v>-1.4548</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7546</v>
+        <v>-0.1593</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4597</v>
+        <v>-1.2377</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2144</v>
+        <v>1.0784</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>3.3208</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>3.3208</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5979</v>
+        <v>-0.425</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2811</v>
+        <v>-0.2667</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3168</v>
+        <v>-0.1583</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0.9414</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8317</v>
+        <v>2.7145</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3869</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9306</v>
+        <v>2.887</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7277</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2029</v>
+        <v>2.9555</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2838</v>
+        <v>1.2657</v>
       </c>
       <c r="H15" t="n">
         <v>0.0926</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3764</v>
+        <v>1.1731</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1245</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3303</v>
+        <v>0.7163</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4548</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1593</v>
+        <v>0.4547</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2377</v>
+        <v>-0.6237</v>
       </c>
       <c r="O15" t="n">
         <v>1.0784</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3208</v>
+        <v>1.7581</v>
       </c>
       <c r="Q15" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.4141</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.1801</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.3208</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.0478</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.1377</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.1855</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.9414</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.7145</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.7731</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1169</v>
+        <v>2.2896</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6752</v>
+        <v>0.9956</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7921</v>
+        <v>1.294</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2657</v>
+        <v>-1.1528</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0926</v>
+        <v>-1.1929</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1731</v>
+        <v>0.0401</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.3982</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7163</v>
+        <v>-1.6526</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09470000000000001</v>
+        <v>1.2544</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4547</v>
+        <v>-0.7546</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6237</v>
+        <v>0.4597</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0784</v>
+        <v>-1.2144</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1842</v>
+        <v>0.6611</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.5621</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3974</v>
+        <v>0.0989</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0.8317</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8478</v>
+        <v>0.6493</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2506</v>
+        <v>-1.1495</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0984</v>
+        <v>1.7988</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1343</v>
@@ -1780,13 +1780,13 @@
         <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0286</v>
+        <v>-0.1699</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1732</v>
+        <v>-0.0721</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2018</v>
+        <v>-0.0978</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3503</v>
+        <v>-1.0231</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2267</v>
+        <v>-3.0356</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8764</v>
+        <v>2.0125</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7839</v>
@@ -1858,13 +1858,13 @@
         <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2615</v>
+        <v>-0.4112</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8118</v>
+        <v>0.0029</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5503</v>
+        <v>-0.4142</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0866</v>
+        <v>-2.986</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1854</v>
+        <v>-2.2753</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9013</v>
+        <v>-0.7106</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7338</v>
@@ -1936,13 +1936,13 @@
         <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0876</v>
+        <v>-0.9869</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6341</v>
+        <v>-0.7241</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4535</v>
+        <v>-0.2629</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6093</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6628</v>
+        <v>-4.0289</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4993</v>
+        <v>-2.8927</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1635</v>
+        <v>-1.1362</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4761</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3355</v>
+        <v>-0.7015</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2105</v>
+        <v>-0.6038</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.125</v>
+        <v>-0.0978</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8279</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6872</v>
+        <v>-5.0959</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3823</v>
+        <v>-4.522</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3049</v>
+        <v>-0.5739</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8377</v>
+        <v>-6.441</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6097</v>
+        <v>-2.0717</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.228</v>
+        <v>-4.3693</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6502</v>
+        <v>-4.9422</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7716</v>
+        <v>-2.3267</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1214</v>
+        <v>-2.6155</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1874</v>
+        <v>-1.4988</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.838</v>
+        <v>0.2551</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3494</v>
+        <v>-1.7538</v>
       </c>
       <c r="P21" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5723</v>
+        <v>-0.0921</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0205</v>
+        <v>-0.0989</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4483</v>
+        <v>0.0068</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8865</v>
+        <v>1.8279</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1052</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0954</v>
+        <v>-5.555</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3309</v>
+        <v>-3.9778</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7645</v>
+        <v>-1.5772</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.441</v>
+        <v>-3.8377</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0717</v>
+        <v>-2.6097</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.3693</v>
+        <v>-1.228</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.9422</v>
+        <v>-1.6502</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3267</v>
+        <v>-1.7716</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6155</v>
+        <v>0.1214</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4988</v>
+        <v>-2.1874</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2551</v>
+        <v>-0.838</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7538</v>
+        <v>-1.3494</v>
       </c>
       <c r="P22" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0917</v>
+        <v>-0.4401</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6161</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1839</v>
+        <v>0.1759</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8279</v>
+        <v>-0.8865</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3321</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.817899999999999</v>
+        <v>-4.818000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-13.2573</v>
       </c>
       <c r="F23" t="n">
-        <v>8.439300000000001</v>
+        <v>8.439399999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-18.5994</v>
@@ -2221,16 +2221,16 @@
         <v>-4.7196</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.959799999999998</v>
+        <v>-9.9598</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.943300000000001</v>
+        <v>-7.9433</v>
       </c>
       <c r="L23" t="n">
         <v>-2.0165</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.639499999999998</v>
+        <v>-8.6395</v>
       </c>
       <c r="N23" t="n">
         <v>-5.936300000000001</v>
@@ -2248,16 +2248,16 @@
         <v>25.3944</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.4937</v>
+        <v>-3.4934</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.993100000000001</v>
+        <v>-1.9931</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5005</v>
+        <v>-1.5008</v>
       </c>
       <c r="V23" t="n">
-        <v>3.601</v>
+        <v>3.601000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>10.4161</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484284_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484284_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.9201</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -799,67 +819,72 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7143</v>
+        <v>1.521</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9224</v>
+        <v>1.521</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6367</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.404</v>
+        <v>1.521</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6624</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7416</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8061</v>
+        <v>1.521</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0639</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7422</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5978</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5984</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1856</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0989</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2846</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-0.3656</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0501</v>
+        <v>-0.8066</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.0787</v>
+        <v>-4.4434</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0286</v>
+        <v>3.6367</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2985</v>
+        <v>0.883</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7536</v>
+        <v>1.3554</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0521</v>
+        <v>-0.4724</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.1174</v>
+        <v>-0.7148</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5519</v>
+        <v>-0.243</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5655</v>
+        <v>-0.4718</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4159</v>
+        <v>1.5978</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7982</v>
+        <v>1.5984</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6176</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.1022</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.8603</v>
+        <v>-3.9069</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9257</v>
+        <v>0.1856</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5752</v>
+        <v>-0.0989</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3505</v>
+        <v>0.2846</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8279</v>
+        <v>0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>3.3238</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6314</v>
+        <v>-1.0501</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0803</v>
+        <v>-5.0787</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5511</v>
+        <v>4.0286</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0706</v>
+        <v>0.2985</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0016</v>
+        <v>-0.7536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9308999999999999</v>
+        <v>1.0521</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7506</v>
+        <v>-3.1174</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7368</v>
+        <v>-2.5519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0138</v>
+        <v>-0.5655</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6798999999999999</v>
+        <v>3.4159</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2648</v>
+        <v>1.7982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9447</v>
+        <v>1.6176</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-5.8603</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0825</v>
+        <v>0.9257</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1225</v>
+        <v>0.5752</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.205</v>
+        <v>0.3505</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6428</v>
+        <v>1.8279</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6428</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8713</v>
+        <v>-1.6314</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6494</v>
+        <v>-1.0803</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2219</v>
+        <v>-0.5511</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2484</v>
+        <v>0.0706</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3671</v>
+        <v>1.0016</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6155</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9733</v>
+        <v>0.7506</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1023</v>
+        <v>0.7368</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0756</v>
+        <v>0.0138</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2751</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>0.2648</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5399</v>
+        <v>-0.9447</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1988</v>
+        <v>-0.0825</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0819</v>
+        <v>0.1225</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2807</v>
+        <v>-0.205</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5758</v>
+        <v>-0.6428</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.6428</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1234,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6553</v>
+        <v>-1.8713</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8433</v>
+        <v>-1.6494</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4986</v>
+        <v>-0.2219</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0237</v>
+        <v>-2.2484</v>
       </c>
       <c r="H10" t="n">
-        <v>2.427</v>
+        <v>0.3671</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4033</v>
+        <v>-2.6155</v>
       </c>
       <c r="J10" t="n">
-        <v>2.313</v>
+        <v>-1.9733</v>
       </c>
       <c r="K10" t="n">
-        <v>2.232</v>
+        <v>0.1023</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-2.0756</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2893</v>
+        <v>-0.2751</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1949</v>
+        <v>0.2648</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4842</v>
+        <v>-0.5399</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,28 +1279,33 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6197</v>
+        <v>-0.1988</v>
       </c>
       <c r="T10" t="n">
-        <v>0.507</v>
+        <v>0.0819</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1127</v>
+        <v>-0.2807</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.2987</v>
+        <v>0.5758</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.2987</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7376</v>
+        <v>-2.6553</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.561</v>
+        <v>1.8433</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8234</v>
+        <v>-4.4986</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9728</v>
+        <v>1.0237</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0565</v>
+        <v>2.427</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9163</v>
+        <v>-1.4033</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3456</v>
+        <v>2.313</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5884</v>
+        <v>2.232</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2428</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3185</v>
+        <v>-1.2893</v>
       </c>
       <c r="N11" t="n">
-        <v>0.645</v>
+        <v>0.1949</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6735</v>
+        <v>-1.4842</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9071</v>
+        <v>0.6197</v>
       </c>
       <c r="T11" t="n">
-        <v>0.137</v>
+        <v>0.507</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7701</v>
+        <v>0.1127</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>-4.2987</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>-4.2987</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.120699999999998</v>
+        <v>-2.7376</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.136600000000001</v>
+        <v>-3.561</v>
       </c>
       <c r="F12" t="n">
-        <v>13.2574</v>
+        <v>0.8234</v>
       </c>
       <c r="G12" t="n">
-        <v>18.5993</v>
+        <v>0.9728</v>
       </c>
       <c r="H12" t="n">
-        <v>13.8798</v>
+        <v>0.0565</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7196</v>
+        <v>0.9163</v>
       </c>
       <c r="J12" t="n">
-        <v>8.639500000000002</v>
+        <v>-0.3456</v>
       </c>
       <c r="K12" t="n">
-        <v>5.936100000000001</v>
+        <v>-0.5884</v>
       </c>
       <c r="L12" t="n">
-        <v>2.7034</v>
+        <v>0.2428</v>
       </c>
       <c r="M12" t="n">
-        <v>9.959900000000001</v>
+        <v>1.3185</v>
       </c>
       <c r="N12" t="n">
-        <v>7.9435</v>
+        <v>0.645</v>
       </c>
       <c r="O12" t="n">
-        <v>2.0164</v>
+        <v>0.6735</v>
       </c>
       <c r="P12" t="n">
-        <v>-13.674</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q12" t="n">
-        <v>-25.3946</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7206</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7961</v>
+        <v>0.9071</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8031</v>
+        <v>0.137</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9932</v>
+        <v>0.7701</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.6011</v>
+        <v>-1.8828</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8151</v>
+        <v>0.5545</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.4163</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. EXPOSITO FORTUNY</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4916</v>
+        <v>5.120799999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3452</v>
+        <v>-8.136600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1464</v>
+        <v>13.2574</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9782999999999999</v>
+        <v>18.5993</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6516</v>
+        <v>13.8798</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6299</v>
+        <v>4.719600000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6121</v>
+        <v>8.6396</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3441</v>
+        <v>5.9362</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9562</v>
+        <v>2.703400000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6338</v>
+        <v>9.959900000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3075</v>
+        <v>7.9435</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6737</v>
+        <v>2.0164</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3674</v>
+        <v>-13.674</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>-25.3946</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2975</v>
+        <v>11.7206</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5137</v>
+        <v>3.7961</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0037</v>
+        <v>1.8031</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5174</v>
+        <v>1.9932</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6596</v>
+        <v>-3.6011</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6596</v>
+        <v>6.8151</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
+        <v>-10.4163</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>G. EXPOSITO FORTUNY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5534</v>
+        <v>4.4916</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3233</v>
+        <v>1.3452</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2301</v>
+        <v>3.1464</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2838</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0926</v>
+        <v>-1.6516</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3764</v>
+        <v>2.6299</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1245</v>
+        <v>1.6121</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3303</v>
+        <v>-0.3441</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.4548</v>
+        <v>1.9562</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1593</v>
+        <v>-0.6338</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2377</v>
+        <v>-1.3075</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0784</v>
+        <v>0.6737</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3208</v>
+        <v>1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3208</v>
+        <v>4.2975</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.425</v>
+        <v>-0.5137</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2667</v>
+        <v>0.0037</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1583</v>
+        <v>-0.5174</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9414</v>
+        <v>2.6596</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7145</v>
+        <v>2.6596</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.887</v>
+        <v>3.5534</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06850000000000001</v>
+        <v>2.3233</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9555</v>
+        <v>1.2301</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2657</v>
+        <v>-0.2838</v>
       </c>
       <c r="H15" t="n">
         <v>0.0926</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1731</v>
+        <v>-0.3764</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.1245</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7163</v>
+        <v>1.3303</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.4548</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4547</v>
+        <v>-0.1593</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6237</v>
+        <v>-1.2377</v>
       </c>
       <c r="O15" t="n">
         <v>1.0784</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>3.3208</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>3.3208</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4141</v>
+        <v>-0.425</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1801</v>
+        <v>-0.2667</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.234</v>
+        <v>-0.1583</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>2.7145</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2896</v>
+        <v>2.887</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9956</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.294</v>
+        <v>2.9555</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1528</v>
+        <v>1.2657</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1929</v>
+        <v>0.0926</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0401</v>
+        <v>1.1731</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3982</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6526</v>
+        <v>0.7163</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2544</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7546</v>
+        <v>0.4547</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4597</v>
+        <v>-0.6237</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2144</v>
+        <v>1.0784</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6611</v>
+        <v>-0.4141</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5621</v>
+        <v>-0.1801</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0989</v>
+        <v>-0.234</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6493</v>
+        <v>2.2896</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1495</v>
+        <v>0.9956</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7988</v>
+        <v>1.294</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1343</v>
+        <v>-1.1528</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.7795</v>
+        <v>-1.1929</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6453</v>
+        <v>0.0401</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3193</v>
+        <v>-0.3982</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.021</v>
+        <v>-1.6526</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7017</v>
+        <v>1.2544</v>
       </c>
       <c r="M17" t="n">
-        <v>0.185</v>
+        <v>-0.7546</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7585</v>
+        <v>0.4597</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9435</v>
+        <v>-1.2144</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9301</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1699</v>
+        <v>0.6611</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0721</v>
+        <v>0.5621</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0978</v>
+        <v>0.0989</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0.8317</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0231</v>
+        <v>0.6493</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0356</v>
+        <v>-1.1495</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0125</v>
+        <v>1.7988</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7839</v>
+        <v>-1.1343</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2162</v>
+        <v>-2.7795</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4323</v>
+        <v>1.6453</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0851</v>
+        <v>-1.3193</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9785</v>
+        <v>-2.021</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1066</v>
+        <v>0.7017</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6988</v>
+        <v>0.185</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2377</v>
+        <v>-0.7585</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5389</v>
+        <v>0.9435</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>2.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4112</v>
+        <v>-0.1699</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0029</v>
+        <v>-0.0721</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4142</v>
+        <v>-0.0978</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.986</v>
+        <v>-1.0231</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2753</v>
+        <v>-3.0356</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7106</v>
+        <v>2.0125</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7338</v>
+        <v>-1.7839</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8475</v>
+        <v>-2.2162</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.8863</v>
+        <v>0.4323</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5512</v>
+        <v>-1.0851</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.284</v>
+        <v>-0.9785</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2673</v>
+        <v>-0.1066</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1826</v>
+        <v>-0.6988</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5636</v>
+        <v>-1.2377</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.619</v>
+        <v>0.5389</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9869</v>
+        <v>-0.4112</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7241</v>
+        <v>0.0029</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2629</v>
+        <v>-0.4142</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0289</v>
+        <v>-2.986</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8927</v>
+        <v>-2.2753</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1362</v>
+        <v>-0.7106</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4761</v>
+        <v>-3.7338</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6958</v>
+        <v>-0.8475</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7803</v>
+        <v>-2.8863</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3122</v>
+        <v>-1.5512</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.284</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7007</v>
+        <v>-1.2673</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1639</v>
+        <v>-2.1826</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0844</v>
+        <v>-0.5636</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-1.619</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>2.3441</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7015</v>
+        <v>-0.9869</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6038</v>
+        <v>-0.7241</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0978</v>
+        <v>-0.2629</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-0.6093</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8279</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0959</v>
+        <v>-4.0289</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.522</v>
+        <v>-2.8927</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5739</v>
+        <v>-1.1362</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.441</v>
+        <v>-2.4761</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0717</v>
+        <v>-0.6958</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.3693</v>
+        <v>-1.7803</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.9422</v>
+        <v>-1.3122</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3267</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6155</v>
+        <v>-0.7007</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4988</v>
+        <v>-1.1639</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2551</v>
+        <v>-0.0844</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7538</v>
+        <v>-1.0795</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0921</v>
+        <v>-0.7015</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0989</v>
+        <v>-0.6038</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0068</v>
+        <v>-0.0978</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8279</v>
+        <v>-1.8279</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3321</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.555</v>
+        <v>-5.0959</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9778</v>
+        <v>-4.522</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5772</v>
+        <v>-0.5739</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8377</v>
+        <v>-6.441</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6097</v>
+        <v>-2.0717</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.228</v>
+        <v>-4.3693</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6502</v>
+        <v>-4.9422</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7716</v>
+        <v>-2.3267</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>-2.6155</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1874</v>
+        <v>-1.4988</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.838</v>
+        <v>0.2551</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3494</v>
+        <v>-1.7538</v>
       </c>
       <c r="P22" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4401</v>
+        <v>-0.0921</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6161</v>
+        <v>-0.0989</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1759</v>
+        <v>0.0068</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8865</v>
+        <v>1.8279</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1052</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-5.555</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.9778</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.5772</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3.8377</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.6097</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.228</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.6502</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.7716</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.1874</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.838</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.4401</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.6161</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484284_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-4.818000000000001</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-13.2573</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>8.439399999999999</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-18.5994</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>-13.8797</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>-4.7196</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>-9.9598</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>-7.9433</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>-2.0165</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-8.6395</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-5.936300000000001</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>-2.7032</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>13.6739</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>25.3944</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>-3.4934</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>-1.9931</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>-1.5008</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>3.601000000000001</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>10.4161</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-6.8151</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
